--- a/NEC_Eventos_Reestruturado_v4.xlsx
+++ b/NEC_Eventos_Reestruturado_v4.xlsx
@@ -696,7 +696,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -746,6 +746,19 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F0FFF0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="001F3864"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00BDD7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -13417,30 +13430,33 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A4:I133">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>=$H4="ATRASADO"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>=AND($H4="PENDENTE",ISNUMBER($F4),$F4&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="0">
+      <formula>=AND($H4="PENDENTE",ISNUMBER($F4),$F4&gt;=TODAY(),$F4&lt;=TODAY()+7)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="0">
+      <formula>=$H4="PENDENTE"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="0">
+      <formula>=$H4="EM ANDAMENTO"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="3" stopIfTrue="0">
+      <formula>=$H4="CONCLUÍDO"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G4:G133">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
         <color rgb="002E75B6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:I133">
-    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
-      <formula>=AND($H4="PENDENTE",ISNUMBER($F4),$F4&lt;TODAY())</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
-      <formula>=$H4="ATRASADO"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="0">
-      <formula>=AND($H4="PENDENTE",ISNUMBER($F4),$F4&gt;=TODAY(),$F4&lt;=TODAY()+7)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="2" stopIfTrue="0">
-      <formula>=$H4="PENDENTE"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" dxfId="3" stopIfTrue="0">
-      <formula>=$H4="CONCLUÍDO"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">

--- a/NEC_Eventos_Reestruturado_v4.xlsx
+++ b/NEC_Eventos_Reestruturado_v4.xlsx
@@ -4057,7 +4057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:O33"/>
+  <dimension ref="B2:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="100" min="1" max="1"/>
@@ -13461,7 +13461,9 @@
         </is>
       </c>
       <c r="E34" s="76" t="n"/>
-      <c r="F34" s="131" t="n"/>
+      <c r="F34" s="131" t="n">
+        <v>46186</v>
+      </c>
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
@@ -13744,7 +13746,9 @@
         </is>
       </c>
       <c r="E43" s="77" t="n"/>
-      <c r="F43" s="131" t="n"/>
+      <c r="F43" s="131" t="n">
+        <v>46191</v>
+      </c>
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
@@ -13992,7 +13996,9 @@
         </is>
       </c>
       <c r="E51" s="77" t="n"/>
-      <c r="F51" s="131" t="n"/>
+      <c r="F51" s="131" t="n">
+        <v>46191</v>
+      </c>
       <c r="G51" s="20" t="n">
         <v>0</v>
       </c>
@@ -14085,7 +14091,9 @@
         </is>
       </c>
       <c r="E54" s="76" t="n"/>
-      <c r="F54" s="131" t="n"/>
+      <c r="F54" s="131" t="n">
+        <v>46168</v>
+      </c>
       <c r="G54" s="20" t="n">
         <v>0</v>
       </c>
@@ -14240,7 +14248,9 @@
         </is>
       </c>
       <c r="E59" s="77" t="n"/>
-      <c r="F59" s="131" t="n"/>
+      <c r="F59" s="131" t="n">
+        <v>46153</v>
+      </c>
       <c r="G59" s="20" t="n">
         <v>0</v>
       </c>
@@ -14271,7 +14281,9 @@
         </is>
       </c>
       <c r="E60" s="76" t="n"/>
-      <c r="F60" s="131" t="n"/>
+      <c r="F60" s="131" t="n">
+        <v>46184</v>
+      </c>
       <c r="G60" s="20" t="n">
         <v>0</v>
       </c>
@@ -14302,7 +14314,9 @@
         </is>
       </c>
       <c r="E61" s="77" t="n"/>
-      <c r="F61" s="131" t="n"/>
+      <c r="F61" s="131" t="n">
+        <v>46213</v>
+      </c>
       <c r="G61" s="20" t="n">
         <v>0</v>
       </c>
@@ -14485,7 +14499,9 @@
         </is>
       </c>
       <c r="E68" s="76" t="n"/>
-      <c r="F68" s="131" t="n"/>
+      <c r="F68" s="131" t="n">
+        <v>46125</v>
+      </c>
       <c r="G68" s="20" t="n">
         <v>0</v>
       </c>
@@ -14516,7 +14532,9 @@
         </is>
       </c>
       <c r="E69" s="77" t="n"/>
-      <c r="F69" s="131" t="n"/>
+      <c r="F69" s="131" t="n">
+        <v>46140</v>
+      </c>
       <c r="G69" s="20" t="n">
         <v>0</v>
       </c>
@@ -14547,7 +14565,9 @@
         </is>
       </c>
       <c r="E70" s="76" t="n"/>
-      <c r="F70" s="131" t="n"/>
+      <c r="F70" s="131" t="n">
+        <v>46185</v>
+      </c>
       <c r="G70" s="20" t="n">
         <v>0</v>
       </c>
@@ -14578,7 +14598,9 @@
         </is>
       </c>
       <c r="E71" s="77" t="n"/>
-      <c r="F71" s="131" t="n"/>
+      <c r="F71" s="131" t="n">
+        <v>46155</v>
+      </c>
       <c r="G71" s="20" t="n">
         <v>0</v>
       </c>
@@ -14609,7 +14631,9 @@
         </is>
       </c>
       <c r="E72" s="76" t="n"/>
-      <c r="F72" s="131" t="n"/>
+      <c r="F72" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G72" s="20" t="n">
         <v>0</v>
       </c>
@@ -14640,7 +14664,9 @@
         </is>
       </c>
       <c r="E73" s="77" t="n"/>
-      <c r="F73" s="131" t="n"/>
+      <c r="F73" s="131" t="n">
+        <v>46185</v>
+      </c>
       <c r="G73" s="20" t="n">
         <v>0</v>
       </c>
@@ -14671,7 +14697,9 @@
         </is>
       </c>
       <c r="E74" s="76" t="n"/>
-      <c r="F74" s="131" t="n"/>
+      <c r="F74" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G74" s="20" t="n">
         <v>0</v>
       </c>
@@ -14702,7 +14730,9 @@
         </is>
       </c>
       <c r="E75" s="77" t="n"/>
-      <c r="F75" s="131" t="n"/>
+      <c r="F75" s="131" t="n">
+        <v>46170</v>
+      </c>
       <c r="G75" s="20" t="n">
         <v>0</v>
       </c>
@@ -14733,7 +14763,9 @@
         </is>
       </c>
       <c r="E76" s="76" t="n"/>
-      <c r="F76" s="131" t="n"/>
+      <c r="F76" s="131" t="n">
+        <v>46201</v>
+      </c>
       <c r="G76" s="20" t="n">
         <v>0</v>
       </c>
@@ -14764,7 +14796,9 @@
         </is>
       </c>
       <c r="E77" s="77" t="n"/>
-      <c r="F77" s="131" t="n"/>
+      <c r="F77" s="131" t="n">
+        <v>46230</v>
+      </c>
       <c r="G77" s="20" t="n">
         <v>0</v>
       </c>
@@ -14791,7 +14825,9 @@
       </c>
       <c r="D78" s="76" t="n"/>
       <c r="E78" s="76" t="n"/>
-      <c r="F78" s="131" t="n"/>
+      <c r="F78" s="131" t="n">
+        <v>46155</v>
+      </c>
       <c r="G78" s="20" t="n">
         <v>0</v>
       </c>
@@ -14818,7 +14854,9 @@
       </c>
       <c r="D79" s="77" t="n"/>
       <c r="E79" s="77" t="n"/>
-      <c r="F79" s="131" t="n"/>
+      <c r="F79" s="131" t="n">
+        <v>46155</v>
+      </c>
       <c r="G79" s="20" t="n">
         <v>0</v>
       </c>
@@ -14849,7 +14887,9 @@
       </c>
       <c r="D80" s="76" t="n"/>
       <c r="E80" s="76" t="n"/>
-      <c r="F80" s="131" t="n"/>
+      <c r="F80" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G80" s="20" t="n">
         <v>0</v>
       </c>
@@ -14880,7 +14920,9 @@
       </c>
       <c r="D81" s="77" t="n"/>
       <c r="E81" s="77" t="n"/>
-      <c r="F81" s="131" t="n"/>
+      <c r="F81" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G81" s="20" t="n">
         <v>0</v>
       </c>
@@ -14911,7 +14953,9 @@
       </c>
       <c r="D82" s="76" t="n"/>
       <c r="E82" s="76" t="n"/>
-      <c r="F82" s="131" t="n"/>
+      <c r="F82" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G82" s="20" t="n">
         <v>0</v>
       </c>
@@ -14942,7 +14986,9 @@
       </c>
       <c r="D83" s="77" t="n"/>
       <c r="E83" s="77" t="n"/>
-      <c r="F83" s="131" t="n"/>
+      <c r="F83" s="131" t="n">
+        <v>46155</v>
+      </c>
       <c r="G83" s="20" t="n">
         <v>0</v>
       </c>
@@ -14973,7 +15019,9 @@
       </c>
       <c r="D84" s="76" t="n"/>
       <c r="E84" s="76" t="n"/>
-      <c r="F84" s="131" t="n"/>
+      <c r="F84" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G84" s="20" t="n">
         <v>0</v>
       </c>
@@ -15004,7 +15052,9 @@
       </c>
       <c r="D85" s="77" t="n"/>
       <c r="E85" s="77" t="n"/>
-      <c r="F85" s="131" t="n"/>
+      <c r="F85" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G85" s="20" t="n">
         <v>0</v>
       </c>
@@ -15035,7 +15085,9 @@
       </c>
       <c r="D86" s="76" t="n"/>
       <c r="E86" s="76" t="n"/>
-      <c r="F86" s="131" t="n"/>
+      <c r="F86" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G86" s="20" t="n">
         <v>0</v>
       </c>
@@ -15066,7 +15118,9 @@
       </c>
       <c r="D87" s="77" t="n"/>
       <c r="E87" s="77" t="n"/>
-      <c r="F87" s="131" t="n"/>
+      <c r="F87" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G87" s="20" t="n">
         <v>0</v>
       </c>
@@ -15097,7 +15151,9 @@
       </c>
       <c r="D88" s="76" t="n"/>
       <c r="E88" s="76" t="n"/>
-      <c r="F88" s="131" t="n"/>
+      <c r="F88" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G88" s="20" t="n">
         <v>0</v>
       </c>
@@ -15128,7 +15184,9 @@
       </c>
       <c r="D89" s="77" t="n"/>
       <c r="E89" s="77" t="n"/>
-      <c r="F89" s="131" t="n"/>
+      <c r="F89" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G89" s="20" t="n">
         <v>0</v>
       </c>
@@ -15159,7 +15217,9 @@
       </c>
       <c r="D90" s="76" t="n"/>
       <c r="E90" s="76" t="n"/>
-      <c r="F90" s="131" t="n"/>
+      <c r="F90" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G90" s="20" t="n">
         <v>0</v>
       </c>
@@ -15190,7 +15250,9 @@
       </c>
       <c r="D91" s="77" t="n"/>
       <c r="E91" s="77" t="n"/>
-      <c r="F91" s="131" t="n"/>
+      <c r="F91" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G91" s="20" t="n">
         <v>0</v>
       </c>
@@ -15221,7 +15283,9 @@
       </c>
       <c r="D92" s="76" t="n"/>
       <c r="E92" s="76" t="n"/>
-      <c r="F92" s="131" t="n"/>
+      <c r="F92" s="131" t="n">
+        <v>46155</v>
+      </c>
       <c r="G92" s="20" t="n">
         <v>0</v>
       </c>
@@ -15252,7 +15316,9 @@
       </c>
       <c r="D93" s="77" t="n"/>
       <c r="E93" s="77" t="n"/>
-      <c r="F93" s="131" t="n"/>
+      <c r="F93" s="131" t="n">
+        <v>46230</v>
+      </c>
       <c r="G93" s="20" t="n">
         <v>0</v>
       </c>
@@ -15283,7 +15349,9 @@
       </c>
       <c r="D94" s="76" t="n"/>
       <c r="E94" s="76" t="n"/>
-      <c r="F94" s="131" t="n"/>
+      <c r="F94" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G94" s="20" t="n">
         <v>0</v>
       </c>
@@ -15315,7 +15383,9 @@
       </c>
       <c r="D95" s="77" t="n"/>
       <c r="E95" s="77" t="n"/>
-      <c r="F95" s="131" t="n"/>
+      <c r="F95" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G95" s="20" t="n">
         <v>0</v>
       </c>
@@ -15470,7 +15540,9 @@
         </is>
       </c>
       <c r="E100" s="76" t="n"/>
-      <c r="F100" s="131" t="n"/>
+      <c r="F100" s="131" t="n">
+        <v>46198</v>
+      </c>
       <c r="G100" s="20" t="n">
         <v>0</v>
       </c>
@@ -15505,7 +15577,9 @@
         </is>
       </c>
       <c r="E101" s="77" t="n"/>
-      <c r="F101" s="131" t="n"/>
+      <c r="F101" s="131" t="n">
+        <v>46198</v>
+      </c>
       <c r="G101" s="20" t="n">
         <v>0</v>
       </c>
@@ -15540,7 +15614,9 @@
         </is>
       </c>
       <c r="E102" s="76" t="n"/>
-      <c r="F102" s="131" t="n"/>
+      <c r="F102" s="131" t="n">
+        <v>46198</v>
+      </c>
       <c r="G102" s="20" t="n">
         <v>0</v>
       </c>
@@ -15571,7 +15647,9 @@
         </is>
       </c>
       <c r="E103" s="77" t="n"/>
-      <c r="F103" s="131" t="n"/>
+      <c r="F103" s="131" t="n">
+        <v>46174</v>
+      </c>
       <c r="G103" s="20" t="n">
         <v>0</v>
       </c>
@@ -15602,7 +15680,9 @@
         </is>
       </c>
       <c r="E104" s="76" t="n"/>
-      <c r="F104" s="131" t="n"/>
+      <c r="F104" s="131" t="n">
+        <v>46205</v>
+      </c>
       <c r="G104" s="20" t="n">
         <v>0</v>
       </c>
@@ -15664,7 +15744,9 @@
         </is>
       </c>
       <c r="E106" s="76" t="n"/>
-      <c r="F106" s="131" t="n"/>
+      <c r="F106" s="131" t="n">
+        <v>46164</v>
+      </c>
       <c r="G106" s="20" t="n">
         <v>0</v>
       </c>
@@ -15726,7 +15808,9 @@
         </is>
       </c>
       <c r="E108" s="76" t="n"/>
-      <c r="F108" s="131" t="n"/>
+      <c r="F108" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G108" s="20" t="n">
         <v>0</v>
       </c>
@@ -15757,7 +15841,9 @@
         </is>
       </c>
       <c r="E109" s="77" t="n"/>
-      <c r="F109" s="131" t="n"/>
+      <c r="F109" s="131" t="n">
+        <v>46209</v>
+      </c>
       <c r="G109" s="20" t="n">
         <v>0</v>
       </c>
@@ -15788,7 +15874,9 @@
         </is>
       </c>
       <c r="E110" s="76" t="n"/>
-      <c r="F110" s="131" t="n"/>
+      <c r="F110" s="131" t="n">
+        <v>46194</v>
+      </c>
       <c r="G110" s="20" t="n">
         <v>0</v>
       </c>
@@ -15823,7 +15911,9 @@
           <t>Time de Marca</t>
         </is>
       </c>
-      <c r="F111" s="131" t="n"/>
+      <c r="F111" s="131" t="n">
+        <v>46185</v>
+      </c>
       <c r="G111" s="20" t="n">
         <v>0.5</v>
       </c>
@@ -15858,7 +15948,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F112" s="131" t="n"/>
+      <c r="F112" s="131" t="n">
+        <v>46185</v>
+      </c>
       <c r="G112" s="20" t="n">
         <v>0</v>
       </c>
@@ -15893,7 +15985,9 @@
           <t>Time de Marca</t>
         </is>
       </c>
-      <c r="F113" s="131" t="n"/>
+      <c r="F113" s="131" t="n">
+        <v>46200</v>
+      </c>
       <c r="G113" s="20" t="n">
         <v>0</v>
       </c>
@@ -15928,7 +16022,9 @@
           <t>Time de Marca</t>
         </is>
       </c>
-      <c r="F114" s="131" t="n"/>
+      <c r="F114" s="131" t="n">
+        <v>46200</v>
+      </c>
       <c r="G114" s="20" t="n">
         <v>0</v>
       </c>
@@ -15963,7 +16059,9 @@
           <t>Time de Marca</t>
         </is>
       </c>
-      <c r="F115" s="131" t="n"/>
+      <c r="F115" s="131" t="n">
+        <v>46200</v>
+      </c>
       <c r="G115" s="20" t="n">
         <v>0</v>
       </c>
@@ -15998,7 +16096,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F116" s="131" t="n"/>
+      <c r="F116" s="131" t="n">
+        <v>46200</v>
+      </c>
       <c r="G116" s="20" t="n">
         <v>0</v>
       </c>
@@ -16033,7 +16133,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F117" s="131" t="n"/>
+      <c r="F117" s="131" t="n">
+        <v>46200</v>
+      </c>
       <c r="G117" s="20" t="n">
         <v>0</v>
       </c>
@@ -16068,7 +16170,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F118" s="131" t="n"/>
+      <c r="F118" s="131" t="n">
+        <v>46215</v>
+      </c>
       <c r="G118" s="20" t="n">
         <v>0</v>
       </c>
@@ -16103,7 +16207,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F119" s="131" t="n"/>
+      <c r="F119" s="131" t="n">
+        <v>46215</v>
+      </c>
       <c r="G119" s="20" t="n">
         <v>0</v>
       </c>
@@ -16138,7 +16244,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F120" s="131" t="n"/>
+      <c r="F120" s="131" t="n">
+        <v>46215</v>
+      </c>
       <c r="G120" s="20" t="n">
         <v>0</v>
       </c>
@@ -16173,7 +16281,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F121" s="131" t="n"/>
+      <c r="F121" s="131" t="n">
+        <v>46230</v>
+      </c>
       <c r="G121" s="20" t="n">
         <v>0</v>
       </c>
@@ -16208,7 +16318,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F122" s="131" t="n"/>
+      <c r="F122" s="131" t="n">
+        <v>46230</v>
+      </c>
       <c r="G122" s="20" t="n">
         <v>0</v>
       </c>
@@ -16243,7 +16355,9 @@
           <t>Time de Marca</t>
         </is>
       </c>
-      <c r="F123" s="131" t="n"/>
+      <c r="F123" s="131" t="n">
+        <v>46230</v>
+      </c>
       <c r="G123" s="20" t="n">
         <v>0</v>
       </c>
@@ -16278,7 +16392,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F124" s="131" t="n"/>
+      <c r="F124" s="131" t="n">
+        <v>46230</v>
+      </c>
       <c r="G124" s="20" t="n">
         <v>0</v>
       </c>
@@ -16313,7 +16429,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F125" s="131" t="n"/>
+      <c r="F125" s="131" t="n">
+        <v>46230</v>
+      </c>
       <c r="G125" s="20" t="n">
         <v>0</v>
       </c>
@@ -16348,7 +16466,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F126" s="131" t="n"/>
+      <c r="F126" s="131" t="n">
+        <v>46245</v>
+      </c>
       <c r="G126" s="20" t="n">
         <v>0</v>
       </c>
@@ -16383,7 +16503,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F127" s="131" t="n"/>
+      <c r="F127" s="131" t="n">
+        <v>46245</v>
+      </c>
       <c r="G127" s="20" t="n">
         <v>0</v>
       </c>
@@ -16418,7 +16540,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F128" s="131" t="n"/>
+      <c r="F128" s="131" t="n">
+        <v>46245</v>
+      </c>
       <c r="G128" s="20" t="n">
         <v>0</v>
       </c>
@@ -16453,7 +16577,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F129" s="131" t="n"/>
+      <c r="F129" s="131" t="n">
+        <v>46245</v>
+      </c>
       <c r="G129" s="20" t="n">
         <v>0</v>
       </c>
@@ -16488,7 +16614,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F130" s="131" t="n"/>
+      <c r="F130" s="131" t="n">
+        <v>46254</v>
+      </c>
       <c r="G130" s="20" t="n">
         <v>0</v>
       </c>
@@ -16523,7 +16651,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F131" s="131" t="n"/>
+      <c r="F131" s="131" t="n">
+        <v>46254</v>
+      </c>
       <c r="G131" s="20" t="n">
         <v>0</v>
       </c>
@@ -16558,7 +16688,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F132" s="131" t="n"/>
+      <c r="F132" s="131" t="n">
+        <v>46254</v>
+      </c>
       <c r="G132" s="20" t="n">
         <v>0</v>
       </c>
@@ -16593,7 +16725,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F133" s="131" t="n"/>
+      <c r="F133" s="131" t="n">
+        <v>46290</v>
+      </c>
       <c r="G133" s="20" t="n">
         <v>0</v>
       </c>
@@ -16628,7 +16762,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F134" s="131" t="n"/>
+      <c r="F134" s="131" t="n">
+        <v>46290</v>
+      </c>
       <c r="G134" s="20" t="n">
         <v>0</v>
       </c>
@@ -16663,7 +16799,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F135" s="131" t="n"/>
+      <c r="F135" s="131" t="n">
+        <v>46290</v>
+      </c>
       <c r="G135" s="20" t="n">
         <v>0</v>
       </c>
@@ -16698,7 +16836,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F136" s="131" t="n"/>
+      <c r="F136" s="131" t="n">
+        <v>46290</v>
+      </c>
       <c r="G136" s="20" t="n">
         <v>0</v>
       </c>
@@ -16733,7 +16873,9 @@
           <t>Eventos</t>
         </is>
       </c>
-      <c r="F137" s="131" t="n"/>
+      <c r="F137" s="131" t="n">
+        <v>46290</v>
+      </c>
       <c r="G137" s="20" t="n">
         <v>0</v>
       </c>
@@ -16764,7 +16906,9 @@
         </is>
       </c>
       <c r="E138" s="77" t="n"/>
-      <c r="F138" s="131" t="n"/>
+      <c r="F138" s="131" t="n">
+        <v>46261</v>
+      </c>
       <c r="G138" s="20" t="n">
         <v>0</v>
       </c>
@@ -16795,7 +16939,9 @@
         </is>
       </c>
       <c r="E139" s="76" t="n"/>
-      <c r="F139" s="131" t="n"/>
+      <c r="F139" s="131" t="n">
+        <v>46233</v>
+      </c>
       <c r="G139" s="20" t="n">
         <v>0.5</v>
       </c>
@@ -16888,7 +17034,9 @@
         </is>
       </c>
       <c r="E142" s="77" t="n"/>
-      <c r="F142" s="131" t="n"/>
+      <c r="F142" s="131" t="n">
+        <v>46302</v>
+      </c>
       <c r="G142" s="20" t="n">
         <v>0</v>
       </c>
@@ -16919,7 +17067,9 @@
         </is>
       </c>
       <c r="E143" s="76" t="n"/>
-      <c r="F143" s="131" t="n"/>
+      <c r="F143" s="131" t="n">
+        <v>46302</v>
+      </c>
       <c r="G143" s="20" t="n">
         <v>0</v>
       </c>
@@ -16950,7 +17100,9 @@
         </is>
       </c>
       <c r="E144" s="77" t="n"/>
-      <c r="F144" s="131" t="n"/>
+      <c r="F144" s="131" t="n">
+        <v>46302</v>
+      </c>
       <c r="G144" s="20" t="n">
         <v>0</v>
       </c>
@@ -16981,7 +17133,9 @@
         </is>
       </c>
       <c r="E145" s="76" t="n"/>
-      <c r="F145" s="131" t="n"/>
+      <c r="F145" s="131" t="n">
+        <v>46278</v>
+      </c>
       <c r="G145" s="20" t="n">
         <v>0</v>
       </c>
@@ -17012,7 +17166,9 @@
         </is>
       </c>
       <c r="E146" s="77" t="n"/>
-      <c r="F146" s="131" t="n"/>
+      <c r="F146" s="131" t="n">
+        <v>46309</v>
+      </c>
       <c r="G146" s="20" t="n">
         <v>0</v>
       </c>

--- a/NEC_Eventos_Reestruturado_v4.xlsx
+++ b/NEC_Eventos_Reestruturado_v4.xlsx
@@ -13465,11 +13465,11 @@
         <v>46186</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I34" s="76" t="n"/>
@@ -13750,11 +13750,11 @@
         <v>46191</v>
       </c>
       <c r="G43" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I43" s="77" t="n"/>
@@ -14000,11 +14000,11 @@
         <v>46191</v>
       </c>
       <c r="G51" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I51" s="77" t="n"/>
@@ -14095,11 +14095,11 @@
         <v>46168</v>
       </c>
       <c r="G54" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I54" s="76" t="n"/>
@@ -14252,11 +14252,11 @@
         <v>46153</v>
       </c>
       <c r="G59" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I59" s="77" t="n"/>
@@ -14285,11 +14285,11 @@
         <v>46184</v>
       </c>
       <c r="G60" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I60" s="76" t="n"/>
@@ -14503,11 +14503,11 @@
         <v>46125</v>
       </c>
       <c r="G68" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I68" s="76" t="n"/>
@@ -14536,11 +14536,11 @@
         <v>46140</v>
       </c>
       <c r="G69" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I69" s="77" t="n"/>
@@ -14569,11 +14569,11 @@
         <v>46185</v>
       </c>
       <c r="G70" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I70" s="76" t="n"/>
@@ -14602,11 +14602,11 @@
         <v>46155</v>
       </c>
       <c r="G71" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I71" s="77" t="n"/>
@@ -14635,11 +14635,11 @@
         <v>46194</v>
       </c>
       <c r="G72" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I72" s="76" t="n"/>
@@ -14668,11 +14668,11 @@
         <v>46185</v>
       </c>
       <c r="G73" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I73" s="77" t="n"/>
@@ -14701,11 +14701,11 @@
         <v>46194</v>
       </c>
       <c r="G74" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I74" s="76" t="n"/>
@@ -14734,11 +14734,11 @@
         <v>46170</v>
       </c>
       <c r="G75" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I75" s="77" t="n"/>
@@ -14829,11 +14829,11 @@
         <v>46155</v>
       </c>
       <c r="G78" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I78" s="76" t="n"/>
@@ -14858,11 +14858,11 @@
         <v>46155</v>
       </c>
       <c r="G79" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I79" s="77" t="inlineStr">
@@ -14891,11 +14891,11 @@
         <v>46194</v>
       </c>
       <c r="G80" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I80" s="76" t="inlineStr">
@@ -14924,11 +14924,11 @@
         <v>46194</v>
       </c>
       <c r="G81" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I81" s="77" t="inlineStr">
@@ -14957,11 +14957,11 @@
         <v>46194</v>
       </c>
       <c r="G82" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I82" s="76" t="inlineStr">
@@ -14990,11 +14990,11 @@
         <v>46155</v>
       </c>
       <c r="G83" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I83" s="77" t="inlineStr">
@@ -15023,11 +15023,11 @@
         <v>46194</v>
       </c>
       <c r="G84" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I84" s="76" t="inlineStr">
@@ -15056,11 +15056,11 @@
         <v>46194</v>
       </c>
       <c r="G85" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I85" s="77" t="inlineStr">
@@ -15089,11 +15089,11 @@
         <v>46194</v>
       </c>
       <c r="G86" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I86" s="76" t="inlineStr">
@@ -15122,11 +15122,11 @@
         <v>46194</v>
       </c>
       <c r="G87" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I87" s="77" t="inlineStr">
@@ -15155,11 +15155,11 @@
         <v>46194</v>
       </c>
       <c r="G88" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I88" s="76" t="inlineStr">
@@ -15188,11 +15188,11 @@
         <v>46194</v>
       </c>
       <c r="G89" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I89" s="77" t="inlineStr">
@@ -15221,11 +15221,11 @@
         <v>46194</v>
       </c>
       <c r="G90" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I90" s="76" t="inlineStr">
@@ -15254,11 +15254,11 @@
         <v>46194</v>
       </c>
       <c r="G91" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I91" s="77" t="inlineStr">
@@ -15287,11 +15287,11 @@
         <v>46155</v>
       </c>
       <c r="G92" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I92" s="76" t="inlineStr">
@@ -15353,11 +15353,11 @@
         <v>46194</v>
       </c>
       <c r="G94" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I94" s="76" t="inlineStr">
@@ -15387,11 +15387,11 @@
         <v>46194</v>
       </c>
       <c r="G95" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I95" s="77" t="n"/>
@@ -15651,11 +15651,11 @@
         <v>46174</v>
       </c>
       <c r="G103" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I103" s="77" t="n"/>
@@ -15748,11 +15748,11 @@
         <v>46164</v>
       </c>
       <c r="G106" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I106" s="76" t="n"/>
@@ -15812,11 +15812,11 @@
         <v>46194</v>
       </c>
       <c r="G108" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I108" s="76" t="n"/>
@@ -15878,11 +15878,11 @@
         <v>46194</v>
       </c>
       <c r="G110" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I110" s="76" t="n"/>
@@ -15915,11 +15915,11 @@
         <v>46185</v>
       </c>
       <c r="G111" s="20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
-          <t>EM ANDAMENTO</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I111" s="77" t="n"/>
@@ -15952,11 +15952,11 @@
         <v>46185</v>
       </c>
       <c r="G112" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="I112" s="76" t="n"/>

--- a/NEC_Eventos_Reestruturado_v4.xlsx
+++ b/NEC_Eventos_Reestruturado_v4.xlsx
@@ -17214,13 +17214,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="D4:D146 E4:E21 E25:E62 E68:E146 I79:I94" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" promptTitle="Responsável" type="list">
-      <formula1>_xlfn._LONGTEXT("1 lâmina - Propaganda ou similar, de produção própria, aprovada pelo CONASEMS,10 unidades,130000,24m²,30 segundos - Em looping no painel de LED,4 unidades,500,00*,6 unidades,Ação promocional - No próprio Estande (se houver),Briefing,Briefing para agênci,C","ontrato (cota),Contrato Palestrantes,Contratos Palestrantes,Coordenador,Documentação Prefeitura (RJ/Gramado),Documentação Prefeitura (SP/RJ/Gramado),EM Aprovada,EM COTA,EM COTA Aprovada")</formula1>
-    </dataValidation>
-    <dataValidation sqref="H4:H146" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" promptTitle="Status" type="list">
+    <dataValidation sqref="H4:H146" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Status" type="list">
       <formula1>"CONCLUÍDO,EM ANDAMENTO,PENDENTE,ATRASADO,-"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F146" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data inválida" error="Insira uma data válida (DD/MM/AAAA) ou deixe em branco. Texto não é permitido nesta coluna." promptTitle="Prazo da Atividade" prompt="Insira a data no formato DD/MM/AAAA.&#10;Deixe em branco se ainda não houver prazo definido." type="date" operator="greaterThanOrEqual">
+    <dataValidation sqref="E4:E146" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Responsável" type="list">
+      <formula1>"Eventos,Fernando Azato,Janaina Silva,Marcio,Time de Marca"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F146" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data inválida" error="Insira uma data válida (DD/MM/AAAA) ou deixe em branco." promptTitle="Prazo da Atividade" prompt="Insira a data no formato DD/MM/AAAA. Deixe em branco se não houver prazo." type="date" operator="greaterThanOrEqual">
       <formula1>43831</formula1>
     </dataValidation>
   </dataValidations>

--- a/NEC_Eventos_Reestruturado_v4.xlsx
+++ b/NEC_Eventos_Reestruturado_v4.xlsx
@@ -22,12 +22,7 @@
     <sheet name="MODELO_CHECKLIST" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="🗺️ ROADMAP" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
-  <definedNames>
-    <definedName name="ExternalData_4" localSheetId="6" hidden="1">PQ_Dashboard!$A$1:$C$13</definedName>
-    <definedName name="ExternalData_3" localSheetId="7" hidden="1">PQ_FinanceiroPendente!$A$1:$Q$3</definedName>
-    <definedName name="ExternalData_2" localSheetId="8" hidden="1">PQ_AtividadesPendentes!$A$1:$K$67</definedName>
-    <definedName name="ExternalData_1" localSheetId="9" hidden="1">PQ_EventosAtivos!$A$1:$AB$15</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -1871,95 +1866,95 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="PQ_Dashboard" displayName="PQ_Dashboard" ref="A1:C13" tableType="queryTable" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="PQ_Dashboard" displayName="PQ_Dashboard" ref="A1:C13" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:C13"/>
   <tableColumns count="3">
-    <tableColumn id="1" uniqueName="1" name="Métrica" queryTableFieldId="1" dataDxfId="54"/>
-    <tableColumn id="2" uniqueName="2" name="Valor" queryTableFieldId="2" dataDxfId="53" dataCellStyle="Currency"/>
-    <tableColumn id="3" uniqueName="3" name="Categoria" queryTableFieldId="3" dataDxfId="52"/>
+    <tableColumn id="1" name="Métrica" dataDxfId="54"/>
+    <tableColumn id="2" name="Valor" dataDxfId="53" dataCellStyle="Currency"/>
+    <tableColumn id="3" name="Categoria" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="PQ_FinanceiroPendente" displayName="PQ_FinanceiroPendente" ref="A1:Q3" tableType="queryTable" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="PQ_FinanceiroPendente" displayName="PQ_FinanceiroPendente" ref="A1:Q3" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:Q3"/>
   <tableColumns count="17">
-    <tableColumn id="1" uniqueName="1" name="ID" queryTableFieldId="1"/>
-    <tableColumn id="2" uniqueName="2" name="Evento" queryTableFieldId="2"/>
-    <tableColumn id="3" uniqueName="3" name="EM (Padrão)" queryTableFieldId="3"/>
-    <tableColumn id="4" uniqueName="4" name="FY" queryTableFieldId="4"/>
-    <tableColumn id="5" uniqueName="5" name="Fornecedor" queryTableFieldId="5"/>
-    <tableColumn id="6" uniqueName="6" name="Tipo de Custo" queryTableFieldId="6"/>
-    <tableColumn id="7" uniqueName="7" name="PO/WF" queryTableFieldId="7"/>
-    <tableColumn id="8" uniqueName="8" name="Orç. Previsto" queryTableFieldId="8"/>
-    <tableColumn id="9" uniqueName="9" name="Real. FY2025" queryTableFieldId="9"/>
-    <tableColumn id="10" uniqueName="10" name="Real. FY2026" queryTableFieldId="10"/>
-    <tableColumn id="11" uniqueName="11" name="Total Evento" queryTableFieldId="11"/>
-    <tableColumn id="12" uniqueName="12" name="Status Pag." queryTableFieldId="12" dataDxfId="51"/>
-    <tableColumn id="13" uniqueName="13" name="Status NF/ND" queryTableFieldId="13" dataDxfId="50"/>
-    <tableColumn id="14" uniqueName="14" name="Observações" queryTableFieldId="14"/>
-    <tableColumn id="15" uniqueName="15" name="Desvio R$" queryTableFieldId="15"/>
-    <tableColumn id="16" uniqueName="16" name="Desvio %" queryTableFieldId="16"/>
-    <tableColumn id="17" uniqueName="17" name="Prioridade" queryTableFieldId="17" dataDxfId="49"/>
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Evento"/>
+    <tableColumn id="3" name="EM (Padrão)"/>
+    <tableColumn id="4" name="FY"/>
+    <tableColumn id="5" name="Fornecedor"/>
+    <tableColumn id="6" name="Tipo de Custo"/>
+    <tableColumn id="7" name="PO/WF"/>
+    <tableColumn id="8" name="Orç. Previsto"/>
+    <tableColumn id="9" name="Real. FY2025"/>
+    <tableColumn id="10" name="Real. FY2026"/>
+    <tableColumn id="11" name="Total Evento"/>
+    <tableColumn id="12" name="Status Pag." dataDxfId="51"/>
+    <tableColumn id="13" name="Status NF/ND" dataDxfId="50"/>
+    <tableColumn id="14" name="Observações"/>
+    <tableColumn id="15" name="Desvio R$"/>
+    <tableColumn id="16" name="Desvio %"/>
+    <tableColumn id="17" name="Prioridade" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="PQ_AtividadesPendentes" displayName="PQ_AtividadesPendentes" ref="A1:K67" tableType="queryTable" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="PQ_AtividadesPendentes" displayName="PQ_AtividadesPendentes" ref="A1:K67" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:K67"/>
   <tableColumns count="11">
-    <tableColumn id="1" uniqueName="1" name="ID" queryTableFieldId="1"/>
-    <tableColumn id="2" uniqueName="2" name="Evento" queryTableFieldId="2"/>
-    <tableColumn id="3" uniqueName="3" name="Etapa" queryTableFieldId="3"/>
-    <tableColumn id="4" uniqueName="4" name="Atividade" queryTableFieldId="4"/>
-    <tableColumn id="5" uniqueName="5" name="Responsável" queryTableFieldId="5" dataDxfId="48"/>
-    <tableColumn id="6" uniqueName="6" name="Prazo" queryTableFieldId="6" dataDxfId="47"/>
-    <tableColumn id="7" uniqueName="7" name="% Conclusão" queryTableFieldId="7"/>
-    <tableColumn id="8" uniqueName="8" name="Status" queryTableFieldId="8" dataDxfId="46"/>
-    <tableColumn id="9" uniqueName="9" name="Observações" queryTableFieldId="9"/>
-    <tableColumn id="10" uniqueName="10" name="Dias até Prazo" queryTableFieldId="10"/>
-    <tableColumn id="11" uniqueName="11" name="Criticidade" queryTableFieldId="11" dataDxfId="45"/>
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Evento"/>
+    <tableColumn id="3" name="Etapa"/>
+    <tableColumn id="4" name="Atividade"/>
+    <tableColumn id="5" name="Responsável" dataDxfId="48"/>
+    <tableColumn id="6" name="Prazo" dataDxfId="47"/>
+    <tableColumn id="7" name="% Conclusão"/>
+    <tableColumn id="8" name="Status" dataDxfId="46"/>
+    <tableColumn id="9" name="Observações"/>
+    <tableColumn id="10" name="Dias até Prazo"/>
+    <tableColumn id="11" name="Criticidade" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="PQ_EventosAtivos" displayName="PQ_EventosAtivos" ref="A1:AB15" tableType="queryTable" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="PQ_EventosAtivos" displayName="PQ_EventosAtivos" ref="A1:AB15" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:AB15"/>
   <tableColumns count="28">
-    <tableColumn id="1" uniqueName="1" name="ID" queryTableFieldId="1"/>
-    <tableColumn id="2" uniqueName="2" name="ID_Unico" queryTableFieldId="2"/>
-    <tableColumn id="3" uniqueName="3" name="Flag" queryTableFieldId="3"/>
-    <tableColumn id="4" uniqueName="4" name="Evento" queryTableFieldId="4"/>
-    <tableColumn id="5" uniqueName="5" name="Tipo" queryTableFieldId="5" dataDxfId="44"/>
-    <tableColumn id="6" uniqueName="6" name="EM Original" queryTableFieldId="6"/>
-    <tableColumn id="7" uniqueName="7" name="Status Evento" queryTableFieldId="7" dataDxfId="43"/>
-    <tableColumn id="8" uniqueName="8" name="Status EM" queryTableFieldId="8"/>
-    <tableColumn id="9" uniqueName="9" name="Ano" queryTableFieldId="9"/>
-    <tableColumn id="10" uniqueName="10" name="Trimestre" queryTableFieldId="10"/>
-    <tableColumn id="11" uniqueName="11" name="Data Início" queryTableFieldId="11" dataDxfId="42"/>
-    <tableColumn id="12" uniqueName="12" name="Data Fim" queryTableFieldId="12" dataDxfId="41"/>
-    <tableColumn id="13" uniqueName="13" name="BU" queryTableFieldId="13" dataDxfId="40"/>
-    <tableColumn id="14" uniqueName="14" name="Produto" queryTableFieldId="14"/>
-    <tableColumn id="15" uniqueName="15" name="Solicitante" queryTableFieldId="15"/>
-    <tableColumn id="16" uniqueName="16" name="Cidade" queryTableFieldId="16" dataDxfId="39"/>
-    <tableColumn id="17" uniqueName="17" name="Formato" queryTableFieldId="17"/>
-    <tableColumn id="18" uniqueName="18" name="Complexidade" queryTableFieldId="18"/>
-    <tableColumn id="19" uniqueName="19" name="Local" queryTableFieldId="19"/>
-    <tableColumn id="20" uniqueName="20" name="Agência" queryTableFieldId="20"/>
-    <tableColumn id="21" uniqueName="21" name="Hotel" queryTableFieldId="21"/>
-    <tableColumn id="22" uniqueName="22" name="Sociedade" queryTableFieldId="22"/>
-    <tableColumn id="23" uniqueName="23" name="Stand" queryTableFieldId="23"/>
-    <tableColumn id="24" uniqueName="24" name="PSs Plan." queryTableFieldId="24"/>
-    <tableColumn id="25" uniqueName="25" name="PSs Pres." queryTableFieldId="25"/>
-    <tableColumn id="26" uniqueName="26" name="Observações" queryTableFieldId="26"/>
-    <tableColumn id="27" uniqueName="27" name="Dias até Evento" queryTableFieldId="27"/>
-    <tableColumn id="28" uniqueName="28" name="Urgência" queryTableFieldId="28" dataDxfId="38"/>
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="ID_Unico"/>
+    <tableColumn id="3" name="Flag"/>
+    <tableColumn id="4" name="Evento"/>
+    <tableColumn id="5" name="Tipo" dataDxfId="44"/>
+    <tableColumn id="6" name="EM Original"/>
+    <tableColumn id="7" name="Status Evento" dataDxfId="43"/>
+    <tableColumn id="8" name="Status EM"/>
+    <tableColumn id="9" name="Ano"/>
+    <tableColumn id="10" name="Trimestre"/>
+    <tableColumn id="11" name="Data Início" dataDxfId="42"/>
+    <tableColumn id="12" name="Data Fim" dataDxfId="41"/>
+    <tableColumn id="13" name="BU" dataDxfId="40"/>
+    <tableColumn id="14" name="Produto"/>
+    <tableColumn id="15" name="Solicitante"/>
+    <tableColumn id="16" name="Cidade" dataDxfId="39"/>
+    <tableColumn id="17" name="Formato"/>
+    <tableColumn id="18" name="Complexidade"/>
+    <tableColumn id="19" name="Local"/>
+    <tableColumn id="20" name="Agência"/>
+    <tableColumn id="21" name="Hotel"/>
+    <tableColumn id="22" name="Sociedade"/>
+    <tableColumn id="23" name="Stand"/>
+    <tableColumn id="24" name="PSs Plan."/>
+    <tableColumn id="25" name="PSs Pres."/>
+    <tableColumn id="26" name="Observações"/>
+    <tableColumn id="27" name="Dias até Evento"/>
+    <tableColumn id="28" name="Urgência" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
